--- a/data/Edison's Scores.xlsx
+++ b/data/Edison's Scores.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="USKids"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="706">
   <si>
     <t>Course</t>
   </si>
@@ -2113,6 +2113,27 @@
   </si>
   <si>
     <t>5,408,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>4,294,3,2,5,Y</t>
+  </si>
+  <si>
+    <t>5,428,6,2,8,X</t>
+  </si>
+  <si>
+    <t>3,140,1,2,3,Y</t>
+  </si>
+  <si>
+    <t>5,413,2,3,5,X</t>
+  </si>
+  <si>
+    <t>4,302,3,3,6,X</t>
+  </si>
+  <si>
+    <t>4,251,3,2,5,X</t>
+  </si>
+  <si>
+    <t>4,295,4,2,6,X</t>
   </si>
 </sst>
 </file>
@@ -6068,19 +6089,45 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="19.5">
-      <c r="A87" s="2"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="12"/>
+      <c r="A87" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C87" s="3">
+        <v>46313</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="M87" s="12">
+        <v>46</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="19.5">
       <c r="A88" s="2"/>
@@ -20902,16 +20949,36 @@
       <c r="T27" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
+      <c r="A28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="5">
+        <v>46314</v>
+      </c>
+      <c r="D28" s="12">
+        <v>31</v>
+      </c>
+      <c r="E28" s="12">
+        <v>3</v>
+      </c>
+      <c r="F28" s="12">
+        <v>2</v>
+      </c>
+      <c r="G28" s="12">
+        <v>2</v>
+      </c>
+      <c r="H28" s="12">
+        <v>3</v>
+      </c>
+      <c r="I28" s="12">
+        <v>4</v>
+      </c>
+      <c r="J28" s="12">
+        <v>46</v>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="12"/>
